--- a/navneleg-demo/students/elevstamdata_navneleg_demo.xlsx
+++ b/navneleg-demo/students/elevstamdata_navneleg_demo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elever" sheetId="1" r:id="Ra1e0d5c2aa78406b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demoelever" sheetId="1" r:id="Re982680c5a404b4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1D4ED8"/>
+        <x:fgColor rgb="FF2563EB"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -78,24 +78,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EleverTable" displayName="EleverTable" ref="A1:J26" headerRowCount="1">
-  <x:tableColumns count="10">
-    <x:tableColumn id="1" name="KortID"/>
-    <x:tableColumn id="2" name="ElevID"/>
-    <x:tableColumn id="3" name="Fornavn"/>
-    <x:tableColumn id="4" name="Efternavn"/>
-    <x:tableColumn id="5" name="FuldeNavn"/>
-    <x:tableColumn id="6" name="Klasse"/>
-    <x:tableColumn id="7" name="Billedfil"/>
-    <x:tableColumn id="8" name="Billedsti"/>
-    <x:tableColumn id="9" name="Bagside"/>
-    <x:tableColumn id="10" name="HumorNote"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -247,19 +229,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="22" customHeight="1">
       <x:c r="A1" s="6" t="str">
         <x:v>KortID</x:v>
       </x:c>
@@ -285,9 +268,12 @@
         <x:v>Billedsti</x:v>
       </x:c>
       <x:c r="I1" s="6" t="str">
+        <x:v>Forside</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="str">
         <x:v>Bagside</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="K1" s="6" t="str">
         <x:v>HumorNote</x:v>
       </x:c>
     </x:row>
@@ -317,9 +303,12 @@
         <x:v>navneleg-demo/students/photos/E001_anker_asteroidsen.png</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
+        <x:v>Astero…</x:v>
+      </x:c>
+      <x:c r="J2" s="12" t="str">
         <x:v>Anker Asteroidsen</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="K2" s="12" t="str">
         <x:v>Kigger ofte ud ad vinduet og kalder det astronomi.</x:v>
       </x:c>
     </x:row>
@@ -349,9 +338,12 @@
         <x:v>navneleg-demo/students/photos/E002_bea_biscuit_bentsen.png</x:v>
       </x:c>
       <x:c r="I3" s="12" t="str">
+        <x:v>Biscui…</x:v>
+      </x:c>
+      <x:c r="J3" s="12" t="str">
         <x:v>Bea Biscuit-Bentsen</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="K3" s="12" t="str">
         <x:v>Har altid en krumme af en god idé i ærmet.</x:v>
       </x:c>
     </x:row>
@@ -381,9 +373,12 @@
         <x:v>navneleg-demo/students/photos/E003_carlo_kommaknudsen.png</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
+        <x:v>Kommak…</x:v>
+      </x:c>
+      <x:c r="J4" s="12" t="str">
         <x:v>Carlo Kommaknudsen</x:v>
       </x:c>
-      <x:c r="J4" s="12" t="str">
+      <x:c r="K4" s="12" t="str">
         <x:v>Sætter kommaer der, hvor andre sætter sig.</x:v>
       </x:c>
     </x:row>
@@ -413,9 +408,12 @@
         <x:v>navneleg-demo/students/photos/E004_dina_dobbeltpunkt.png</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
+        <x:v>Dobbel…</x:v>
+      </x:c>
+      <x:c r="J5" s="12" t="str">
         <x:v>Dina Dobbeltpunkt</x:v>
       </x:c>
-      <x:c r="J5" s="12" t="str">
+      <x:c r="K5" s="12" t="str">
         <x:v>Starter alle forklaringer med: 'Hør her:'</x:v>
       </x:c>
     </x:row>
@@ -445,9 +443,12 @@
         <x:v>navneleg-demo/students/photos/E005_emil_energidriksen.png</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
+        <x:v>Energi…</x:v>
+      </x:c>
+      <x:c r="J6" s="12" t="str">
         <x:v>Emil Energidriksen</x:v>
       </x:c>
-      <x:c r="J6" s="12" t="str">
+      <x:c r="K6" s="12" t="str">
         <x:v>Kan løbe en besked hurtigere end Aula kan åbne.</x:v>
       </x:c>
     </x:row>
@@ -477,9 +478,12 @@
         <x:v>navneleg-demo/students/photos/E006_freja_fodboldfod.png</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
+        <x:v>Fodbol…</x:v>
+      </x:c>
+      <x:c r="J7" s="12" t="str">
         <x:v>Freja Fodboldfod</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="str">
+      <x:c r="K7" s="12" t="str">
         <x:v>Mener at gruppearbejde er bedst med offside-regel.</x:v>
       </x:c>
     </x:row>
@@ -509,9 +513,12 @@
         <x:v>navneleg-demo/students/photos/E007_gustav_gummistoevle.png</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
+        <x:v>Gummis…</x:v>
+      </x:c>
+      <x:c r="J8" s="12" t="str">
         <x:v>Gustav Gummistøvle</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="str">
+      <x:c r="K8" s="12" t="str">
         <x:v>Forberedt på regn, sne og pludselige diktater.</x:v>
       </x:c>
     </x:row>
@@ -541,9 +548,12 @@
         <x:v>navneleg-demo/students/photos/E008_hilda_hattehat.png</x:v>
       </x:c>
       <x:c r="I9" s="12" t="str">
+        <x:v>Hatteh…</x:v>
+      </x:c>
+      <x:c r="J9" s="12" t="str">
         <x:v>Hilda Hattehat</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="str">
+      <x:c r="K9" s="12" t="str">
         <x:v>Har en hat til hver grammatikregel.</x:v>
       </x:c>
     </x:row>
@@ -573,9 +583,12 @@
         <x:v>navneleg-demo/students/photos/E009_ivan_ildflue.png</x:v>
       </x:c>
       <x:c r="I10" s="12" t="str">
+        <x:v>Ildflu…</x:v>
+      </x:c>
+      <x:c r="J10" s="12" t="str">
         <x:v>Ivan Ildflue</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="str">
+      <x:c r="K10" s="12" t="str">
         <x:v>Lyser op i mørke lokaler og lange moduler.</x:v>
       </x:c>
     </x:row>
@@ -605,9 +618,12 @@
         <x:v>navneleg-demo/students/photos/E010_juno_jordbaer_jensen.png</x:v>
       </x:c>
       <x:c r="I11" s="12" t="str">
+        <x:v>Jordbæ…</x:v>
+      </x:c>
+      <x:c r="J11" s="12" t="str">
         <x:v>Juno Jordbær-Jensen</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="str">
+      <x:c r="K11" s="12" t="str">
         <x:v>Kan finde en rød tråd i både stil og syltetøj.</x:v>
       </x:c>
     </x:row>
@@ -637,9 +653,12 @@
         <x:v>navneleg-demo/students/photos/E011_karla_kaktus.png</x:v>
       </x:c>
       <x:c r="I12" s="12" t="str">
+        <x:v>Kak…</x:v>
+      </x:c>
+      <x:c r="J12" s="12" t="str">
         <x:v>Karla Kaktus</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="str">
+      <x:c r="K12" s="12" t="str">
         <x:v>Stikker lidt, men kun når afleveringen mangler navn.</x:v>
       </x:c>
     </x:row>
@@ -669,9 +688,12 @@
         <x:v>navneleg-demo/students/photos/E012_leo_lommefilosof.png</x:v>
       </x:c>
       <x:c r="I13" s="12" t="str">
+        <x:v>Lommef…</x:v>
+      </x:c>
+      <x:c r="J13" s="12" t="str">
         <x:v>Leo Lommefilosof</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="str">
+      <x:c r="K13" s="12" t="str">
         <x:v>Spørger: 'Men hvad ER egentlig frikvarter?'</x:v>
       </x:c>
     </x:row>
@@ -701,9 +723,12 @@
         <x:v>navneleg-demo/students/photos/E013_mira_marmelade.png</x:v>
       </x:c>
       <x:c r="I14" s="12" t="str">
+        <x:v>Marmel…</x:v>
+      </x:c>
+      <x:c r="J14" s="12" t="str">
         <x:v>Mira Marmelade</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="str">
+      <x:c r="K14" s="12" t="str">
         <x:v>Spreder ro på brødet og i klassen.</x:v>
       </x:c>
     </x:row>
@@ -733,9 +758,12 @@
         <x:v>navneleg-demo/students/photos/E014_noah_noerkle.png</x:v>
       </x:c>
       <x:c r="I15" s="12" t="str">
+        <x:v>Nør…</x:v>
+      </x:c>
+      <x:c r="J15" s="12" t="str">
         <x:v>Noah Nørkle</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="str">
+      <x:c r="K15" s="12" t="str">
         <x:v>Bygger løsninger af tape, tegnestifter og optimisme.</x:v>
       </x:c>
     </x:row>
@@ -765,9 +793,12 @@
         <x:v>navneleg-demo/students/photos/E015_oda_overspringsen.png</x:v>
       </x:c>
       <x:c r="I16" s="12" t="str">
+        <x:v>Oversp…</x:v>
+      </x:c>
+      <x:c r="J16" s="12" t="str">
         <x:v>Oda Overspringsen</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="str">
+      <x:c r="K16" s="12" t="str">
         <x:v>Skulle lige noget vigtigt, men nåede det alligevel.</x:v>
       </x:c>
     </x:row>
@@ -797,9 +828,12 @@
         <x:v>navneleg-demo/students/photos/E016_pelle_papirfly.png</x:v>
       </x:c>
       <x:c r="I17" s="12" t="str">
+        <x:v>Papirf…</x:v>
+      </x:c>
+      <x:c r="J17" s="12" t="str">
         <x:v>Pelle Papirfly</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="str">
+      <x:c r="K17" s="12" t="str">
         <x:v>Afleverer helst i aerodynamisk format.</x:v>
       </x:c>
     </x:row>
@@ -829,9 +863,12 @@
         <x:v>navneleg-demo/students/photos/E017_quinten_quizgaard.png</x:v>
       </x:c>
       <x:c r="I18" s="12" t="str">
+        <x:v>Quizga…</x:v>
+      </x:c>
+      <x:c r="J18" s="12" t="str">
         <x:v>Quinten Quizgaard</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="str">
+      <x:c r="K18" s="12" t="str">
         <x:v>Ved svaret før spørgsmålet er færdigt.</x:v>
       </x:c>
     </x:row>
@@ -861,9 +898,12 @@
         <x:v>navneleg-demo/students/photos/E018_rosa_rundstykke.png</x:v>
       </x:c>
       <x:c r="I19" s="12" t="str">
+        <x:v>Rundst…</x:v>
+      </x:c>
+      <x:c r="J19" s="12" t="str">
         <x:v>Rosa Rundstykke</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="str">
+      <x:c r="K19" s="12" t="str">
         <x:v>Møder ind med sprød stemning og smør på humøret.</x:v>
       </x:c>
     </x:row>
@@ -893,9 +933,12 @@
         <x:v>navneleg-demo/students/photos/E019_silas_snebold.png</x:v>
       </x:c>
       <x:c r="I20" s="12" t="str">
+        <x:v>Snebol…</x:v>
+      </x:c>
+      <x:c r="J20" s="12" t="str">
         <x:v>Silas Snebold</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="str">
+      <x:c r="K20" s="12" t="str">
         <x:v>Kaster med idéer, ikke med skyld.</x:v>
       </x:c>
     </x:row>
@@ -925,9 +968,12 @@
         <x:v>navneleg-demo/students/photos/E020_tilde_tidsmaskine.png</x:v>
       </x:c>
       <x:c r="I21" s="12" t="str">
+        <x:v>Tidsma…</x:v>
+      </x:c>
+      <x:c r="J21" s="12" t="str">
         <x:v>Tilde Tidsmaskine</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="str">
+      <x:c r="K21" s="12" t="str">
         <x:v>Kommer for sent, men påstår hun var tidligt i 2034.</x:v>
       </x:c>
     </x:row>
@@ -957,9 +1003,12 @@
         <x:v>navneleg-demo/students/photos/E021_ulrik_uglebjerg.png</x:v>
       </x:c>
       <x:c r="I22" s="12" t="str">
+        <x:v>Uglebj…</x:v>
+      </x:c>
+      <x:c r="J22" s="12" t="str">
         <x:v>Ulrik Uglebjerg</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="str">
+      <x:c r="K22" s="12" t="str">
         <x:v>Vågen når andre lukker fanerne.</x:v>
       </x:c>
     </x:row>
@@ -989,9 +1038,12 @@
         <x:v>navneleg-demo/students/photos/E022_vera_vaffelvang.png</x:v>
       </x:c>
       <x:c r="I23" s="12" t="str">
+        <x:v>Vaffel…</x:v>
+      </x:c>
+      <x:c r="J23" s="12" t="str">
         <x:v>Vera Vaffelvang</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="str">
+      <x:c r="K23" s="12" t="str">
         <x:v>Kan gøre enhver diskussion firkantet på den gode måde.</x:v>
       </x:c>
     </x:row>
@@ -1021,9 +1073,12 @@
         <x:v>navneleg-demo/students/photos/E023_wilma_wifi.png</x:v>
       </x:c>
       <x:c r="I24" s="12" t="str">
+        <x:v>WiF…</x:v>
+      </x:c>
+      <x:c r="J24" s="12" t="str">
         <x:v>Wilma WiFi</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="str">
+      <x:c r="K24" s="12" t="str">
         <x:v>Forsvinder kort, men forbinder altid igen.</x:v>
       </x:c>
     </x:row>
@@ -1053,9 +1108,12 @@
         <x:v>navneleg-demo/students/photos/E024_xander_xylofon.png</x:v>
       </x:c>
       <x:c r="I25" s="12" t="str">
+        <x:v>Xylofo…</x:v>
+      </x:c>
+      <x:c r="J25" s="12" t="str">
         <x:v>Xander Xylofon</x:v>
       </x:c>
-      <x:c r="J25" s="12" t="str">
+      <x:c r="K25" s="12" t="str">
         <x:v>Tænker i toner, selv i matematik.</x:v>
       </x:c>
     </x:row>
@@ -1085,16 +1143,16 @@
         <x:v>navneleg-demo/students/photos/E025_yrsa_yoghurt.png</x:v>
       </x:c>
       <x:c r="I26" s="12" t="str">
+        <x:v>Yoghur…</x:v>
+      </x:c>
+      <x:c r="J26" s="12" t="str">
         <x:v>Yrsa Yoghurt</x:v>
       </x:c>
-      <x:c r="J26" s="12" t="str">
+      <x:c r="K26" s="12" t="str">
         <x:v>Holder hovedet koldt og kulturen levende.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R134ff0e60ec34467"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/navneleg-demo/students/elevstamdata_navneleg_demo.xlsx
+++ b/navneleg-demo/students/elevstamdata_navneleg_demo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demoelever" sheetId="1" r:id="Re982680c5a404b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Navneleg" sheetId="1" r:id="Ra5fb6ccaa5754f1c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF2563EB"/>
+        <x:fgColor rgb="FF1D4ED8"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -45,30 +45,24 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -78,6 +72,25 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NavnelegTable" displayName="NavnelegTable" ref="A1:K26" headerRowCount="1">
+  <x:tableColumns count="11">
+    <x:tableColumn id="1" name="KortID"/>
+    <x:tableColumn id="2" name="ElevID"/>
+    <x:tableColumn id="3" name="Fornavn"/>
+    <x:tableColumn id="4" name="Efternavn"/>
+    <x:tableColumn id="5" name="FuldeNavn"/>
+    <x:tableColumn id="6" name="Klasse"/>
+    <x:tableColumn id="7" name="Billedfil"/>
+    <x:tableColumn id="8" name="Billedsti"/>
+    <x:tableColumn id="9" name="Forside"/>
+    <x:tableColumn id="10" name="Bagside"/>
+    <x:tableColumn id="11" name="HumorNote"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -229,930 +242,933 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+      <x:c r="A1" s="5" t="str">
         <x:v>KortID</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="5" t="str">
         <x:v>ElevID</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="str">
+      <x:c r="C1" s="5" t="str">
         <x:v>Fornavn</x:v>
       </x:c>
-      <x:c r="D1" s="6" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>Efternavn</x:v>
       </x:c>
-      <x:c r="E1" s="6" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>FuldeNavn</x:v>
       </x:c>
-      <x:c r="F1" s="6" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Klasse</x:v>
       </x:c>
-      <x:c r="G1" s="6" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>Billedfil</x:v>
       </x:c>
-      <x:c r="H1" s="6" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>Billedsti</x:v>
       </x:c>
-      <x:c r="I1" s="6" t="str">
+      <x:c r="I1" s="5" t="str">
         <x:v>Forside</x:v>
       </x:c>
-      <x:c r="J1" s="6" t="str">
+      <x:c r="J1" s="5" t="str">
         <x:v>Bagside</x:v>
       </x:c>
-      <x:c r="K1" s="6" t="str">
+      <x:c r="K1" s="5" t="str">
         <x:v>HumorNote</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="10" t="str">
         <x:v>E001</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="10" t="str">
         <x:v>E001</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="10" t="str">
         <x:v>Anker</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="10" t="str">
         <x:v>Asteroidsen</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="10" t="str">
         <x:v>Anker Asteroidsen</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="10" t="str">
         <x:v>8A</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="10" t="str">
         <x:v>E001_anker_asteroidsen.png</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E001_anker_asteroidsen.png</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="10" t="str">
         <x:v>Astero…</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="10" t="str">
         <x:v>Anker Asteroidsen</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="10" t="str">
         <x:v>Kigger ofte ud ad vinduet og kalder det astronomi.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="12" t="str">
+      <x:c r="A3" s="10" t="str">
         <x:v>E002</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
+      <x:c r="B3" s="10" t="str">
         <x:v>E002</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="str">
+      <x:c r="C3" s="10" t="str">
         <x:v>Bea</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="str">
+      <x:c r="D3" s="10" t="str">
         <x:v>Biscuit-Bentsen</x:v>
       </x:c>
-      <x:c r="E3" s="12" t="str">
+      <x:c r="E3" s="10" t="str">
         <x:v>Bea Biscuit-Bentsen</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="str">
+      <x:c r="F3" s="10" t="str">
         <x:v>8A</x:v>
       </x:c>
-      <x:c r="G3" s="12" t="str">
+      <x:c r="G3" s="10" t="str">
         <x:v>E002_bea_biscuit_bentsen.png</x:v>
       </x:c>
-      <x:c r="H3" s="12" t="str">
+      <x:c r="H3" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E002_bea_biscuit_bentsen.png</x:v>
       </x:c>
-      <x:c r="I3" s="12" t="str">
+      <x:c r="I3" s="10" t="str">
         <x:v>Biscui…</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="str">
+      <x:c r="J3" s="10" t="str">
         <x:v>Bea Biscuit-Bentsen</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="str">
+      <x:c r="K3" s="10" t="str">
         <x:v>Har altid en krumme af en god idé i ærmet.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="12" t="str">
+      <x:c r="A4" s="10" t="str">
         <x:v>E003</x:v>
       </x:c>
-      <x:c r="B4" s="12" t="str">
+      <x:c r="B4" s="10" t="str">
         <x:v>E003</x:v>
       </x:c>
-      <x:c r="C4" s="12" t="str">
+      <x:c r="C4" s="10" t="str">
         <x:v>Carlo</x:v>
       </x:c>
-      <x:c r="D4" s="12" t="str">
+      <x:c r="D4" s="10" t="str">
         <x:v>Kommaknudsen</x:v>
       </x:c>
-      <x:c r="E4" s="12" t="str">
+      <x:c r="E4" s="10" t="str">
         <x:v>Carlo Kommaknudsen</x:v>
       </x:c>
-      <x:c r="F4" s="12" t="str">
+      <x:c r="F4" s="10" t="str">
         <x:v>8A</x:v>
       </x:c>
-      <x:c r="G4" s="12" t="str">
+      <x:c r="G4" s="10" t="str">
         <x:v>E003_carlo_kommaknudsen.png</x:v>
       </x:c>
-      <x:c r="H4" s="12" t="str">
+      <x:c r="H4" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E003_carlo_kommaknudsen.png</x:v>
       </x:c>
-      <x:c r="I4" s="12" t="str">
+      <x:c r="I4" s="10" t="str">
         <x:v>Kommak…</x:v>
       </x:c>
-      <x:c r="J4" s="12" t="str">
+      <x:c r="J4" s="10" t="str">
         <x:v>Carlo Kommaknudsen</x:v>
       </x:c>
-      <x:c r="K4" s="12" t="str">
+      <x:c r="K4" s="10" t="str">
         <x:v>Sætter kommaer der, hvor andre sætter sig.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="12" t="str">
+      <x:c r="A5" s="10" t="str">
         <x:v>E004</x:v>
       </x:c>
-      <x:c r="B5" s="12" t="str">
+      <x:c r="B5" s="10" t="str">
         <x:v>E004</x:v>
       </x:c>
-      <x:c r="C5" s="12" t="str">
+      <x:c r="C5" s="10" t="str">
         <x:v>Dina</x:v>
       </x:c>
-      <x:c r="D5" s="12" t="str">
+      <x:c r="D5" s="10" t="str">
         <x:v>Dobbeltpunkt</x:v>
       </x:c>
-      <x:c r="E5" s="12" t="str">
+      <x:c r="E5" s="10" t="str">
         <x:v>Dina Dobbeltpunkt</x:v>
       </x:c>
-      <x:c r="F5" s="12" t="str">
+      <x:c r="F5" s="10" t="str">
         <x:v>8A</x:v>
       </x:c>
-      <x:c r="G5" s="12" t="str">
+      <x:c r="G5" s="10" t="str">
         <x:v>E004_dina_dobbeltpunkt.png</x:v>
       </x:c>
-      <x:c r="H5" s="12" t="str">
+      <x:c r="H5" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E004_dina_dobbeltpunkt.png</x:v>
       </x:c>
-      <x:c r="I5" s="12" t="str">
+      <x:c r="I5" s="10" t="str">
         <x:v>Dobbel…</x:v>
       </x:c>
-      <x:c r="J5" s="12" t="str">
+      <x:c r="J5" s="10" t="str">
         <x:v>Dina Dobbeltpunkt</x:v>
       </x:c>
-      <x:c r="K5" s="12" t="str">
+      <x:c r="K5" s="10" t="str">
         <x:v>Starter alle forklaringer med: 'Hør her:'</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="12" t="str">
+      <x:c r="A6" s="10" t="str">
         <x:v>E005</x:v>
       </x:c>
-      <x:c r="B6" s="12" t="str">
+      <x:c r="B6" s="10" t="str">
         <x:v>E005</x:v>
       </x:c>
-      <x:c r="C6" s="12" t="str">
+      <x:c r="C6" s="10" t="str">
         <x:v>Emil</x:v>
       </x:c>
-      <x:c r="D6" s="12" t="str">
+      <x:c r="D6" s="10" t="str">
         <x:v>Energidriksen</x:v>
       </x:c>
-      <x:c r="E6" s="12" t="str">
+      <x:c r="E6" s="10" t="str">
         <x:v>Emil Energidriksen</x:v>
       </x:c>
-      <x:c r="F6" s="12" t="str">
+      <x:c r="F6" s="10" t="str">
         <x:v>8A</x:v>
       </x:c>
-      <x:c r="G6" s="12" t="str">
+      <x:c r="G6" s="10" t="str">
         <x:v>E005_emil_energidriksen.png</x:v>
       </x:c>
-      <x:c r="H6" s="12" t="str">
+      <x:c r="H6" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E005_emil_energidriksen.png</x:v>
       </x:c>
-      <x:c r="I6" s="12" t="str">
+      <x:c r="I6" s="10" t="str">
         <x:v>Energi…</x:v>
       </x:c>
-      <x:c r="J6" s="12" t="str">
+      <x:c r="J6" s="10" t="str">
         <x:v>Emil Energidriksen</x:v>
       </x:c>
-      <x:c r="K6" s="12" t="str">
+      <x:c r="K6" s="10" t="str">
         <x:v>Kan løbe en besked hurtigere end Aula kan åbne.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="12" t="str">
+      <x:c r="A7" s="10" t="str">
         <x:v>E006</x:v>
       </x:c>
-      <x:c r="B7" s="12" t="str">
+      <x:c r="B7" s="10" t="str">
         <x:v>E006</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="str">
+      <x:c r="C7" s="10" t="str">
         <x:v>Freja</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="str">
+      <x:c r="D7" s="10" t="str">
         <x:v>Fodboldfod</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="str">
+      <x:c r="E7" s="10" t="str">
         <x:v>Freja Fodboldfod</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="str">
+      <x:c r="F7" s="10" t="str">
         <x:v>8B</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="str">
+      <x:c r="G7" s="10" t="str">
         <x:v>E006_freja_fodboldfod.png</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="str">
+      <x:c r="H7" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E006_freja_fodboldfod.png</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="str">
+      <x:c r="I7" s="10" t="str">
         <x:v>Fodbol…</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="str">
+      <x:c r="J7" s="10" t="str">
         <x:v>Freja Fodboldfod</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="str">
+      <x:c r="K7" s="10" t="str">
         <x:v>Mener at gruppearbejde er bedst med offside-regel.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="12" t="str">
+      <x:c r="A8" s="10" t="str">
         <x:v>E007</x:v>
       </x:c>
-      <x:c r="B8" s="12" t="str">
+      <x:c r="B8" s="10" t="str">
         <x:v>E007</x:v>
       </x:c>
-      <x:c r="C8" s="12" t="str">
+      <x:c r="C8" s="10" t="str">
         <x:v>Gustav</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="str">
+      <x:c r="D8" s="10" t="str">
         <x:v>Gummistøvle</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="str">
+      <x:c r="E8" s="10" t="str">
         <x:v>Gustav Gummistøvle</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="str">
+      <x:c r="F8" s="10" t="str">
         <x:v>8B</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="str">
+      <x:c r="G8" s="10" t="str">
         <x:v>E007_gustav_gummistoevle.png</x:v>
       </x:c>
-      <x:c r="H8" s="12" t="str">
+      <x:c r="H8" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E007_gustav_gummistoevle.png</x:v>
       </x:c>
-      <x:c r="I8" s="12" t="str">
+      <x:c r="I8" s="10" t="str">
         <x:v>Gummis…</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="str">
+      <x:c r="J8" s="10" t="str">
         <x:v>Gustav Gummistøvle</x:v>
       </x:c>
-      <x:c r="K8" s="12" t="str">
+      <x:c r="K8" s="10" t="str">
         <x:v>Forberedt på regn, sne og pludselige diktater.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="12" t="str">
+      <x:c r="A9" s="10" t="str">
         <x:v>E008</x:v>
       </x:c>
-      <x:c r="B9" s="12" t="str">
+      <x:c r="B9" s="10" t="str">
         <x:v>E008</x:v>
       </x:c>
-      <x:c r="C9" s="12" t="str">
+      <x:c r="C9" s="10" t="str">
         <x:v>Hilda</x:v>
       </x:c>
-      <x:c r="D9" s="12" t="str">
+      <x:c r="D9" s="10" t="str">
         <x:v>Hattehat</x:v>
       </x:c>
-      <x:c r="E9" s="12" t="str">
+      <x:c r="E9" s="10" t="str">
         <x:v>Hilda Hattehat</x:v>
       </x:c>
-      <x:c r="F9" s="12" t="str">
+      <x:c r="F9" s="10" t="str">
         <x:v>8B</x:v>
       </x:c>
-      <x:c r="G9" s="12" t="str">
+      <x:c r="G9" s="10" t="str">
         <x:v>E008_hilda_hattehat.png</x:v>
       </x:c>
-      <x:c r="H9" s="12" t="str">
+      <x:c r="H9" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E008_hilda_hattehat.png</x:v>
       </x:c>
-      <x:c r="I9" s="12" t="str">
+      <x:c r="I9" s="10" t="str">
         <x:v>Hatteh…</x:v>
       </x:c>
-      <x:c r="J9" s="12" t="str">
+      <x:c r="J9" s="10" t="str">
         <x:v>Hilda Hattehat</x:v>
       </x:c>
-      <x:c r="K9" s="12" t="str">
+      <x:c r="K9" s="10" t="str">
         <x:v>Har en hat til hver grammatikregel.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="12" t="str">
+      <x:c r="A10" s="10" t="str">
         <x:v>E009</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="str">
+      <x:c r="B10" s="10" t="str">
         <x:v>E009</x:v>
       </x:c>
-      <x:c r="C10" s="12" t="str">
+      <x:c r="C10" s="10" t="str">
         <x:v>Ivan</x:v>
       </x:c>
-      <x:c r="D10" s="12" t="str">
+      <x:c r="D10" s="10" t="str">
         <x:v>Ildflue</x:v>
       </x:c>
-      <x:c r="E10" s="12" t="str">
+      <x:c r="E10" s="10" t="str">
         <x:v>Ivan Ildflue</x:v>
       </x:c>
-      <x:c r="F10" s="12" t="str">
+      <x:c r="F10" s="10" t="str">
         <x:v>8B</x:v>
       </x:c>
-      <x:c r="G10" s="12" t="str">
+      <x:c r="G10" s="10" t="str">
         <x:v>E009_ivan_ildflue.png</x:v>
       </x:c>
-      <x:c r="H10" s="12" t="str">
+      <x:c r="H10" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E009_ivan_ildflue.png</x:v>
       </x:c>
-      <x:c r="I10" s="12" t="str">
+      <x:c r="I10" s="10" t="str">
         <x:v>Ildflu…</x:v>
       </x:c>
-      <x:c r="J10" s="12" t="str">
+      <x:c r="J10" s="10" t="str">
         <x:v>Ivan Ildflue</x:v>
       </x:c>
-      <x:c r="K10" s="12" t="str">
+      <x:c r="K10" s="10" t="str">
         <x:v>Lyser op i mørke lokaler og lange moduler.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="12" t="str">
+      <x:c r="A11" s="10" t="str">
         <x:v>E010</x:v>
       </x:c>
-      <x:c r="B11" s="12" t="str">
+      <x:c r="B11" s="10" t="str">
         <x:v>E010</x:v>
       </x:c>
-      <x:c r="C11" s="12" t="str">
+      <x:c r="C11" s="10" t="str">
         <x:v>Juno</x:v>
       </x:c>
-      <x:c r="D11" s="12" t="str">
+      <x:c r="D11" s="10" t="str">
         <x:v>Jordbær-Jensen</x:v>
       </x:c>
-      <x:c r="E11" s="12" t="str">
+      <x:c r="E11" s="10" t="str">
         <x:v>Juno Jordbær-Jensen</x:v>
       </x:c>
-      <x:c r="F11" s="12" t="str">
+      <x:c r="F11" s="10" t="str">
         <x:v>8B</x:v>
       </x:c>
-      <x:c r="G11" s="12" t="str">
+      <x:c r="G11" s="10" t="str">
         <x:v>E010_juno_jordbaer_jensen.png</x:v>
       </x:c>
-      <x:c r="H11" s="12" t="str">
+      <x:c r="H11" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E010_juno_jordbaer_jensen.png</x:v>
       </x:c>
-      <x:c r="I11" s="12" t="str">
+      <x:c r="I11" s="10" t="str">
         <x:v>Jordbæ…</x:v>
       </x:c>
-      <x:c r="J11" s="12" t="str">
+      <x:c r="J11" s="10" t="str">
         <x:v>Juno Jordbær-Jensen</x:v>
       </x:c>
-      <x:c r="K11" s="12" t="str">
+      <x:c r="K11" s="10" t="str">
         <x:v>Kan finde en rød tråd i både stil og syltetøj.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="12" t="str">
+      <x:c r="A12" s="10" t="str">
         <x:v>E011</x:v>
       </x:c>
-      <x:c r="B12" s="12" t="str">
+      <x:c r="B12" s="10" t="str">
         <x:v>E011</x:v>
       </x:c>
-      <x:c r="C12" s="12" t="str">
+      <x:c r="C12" s="10" t="str">
         <x:v>Karla</x:v>
       </x:c>
-      <x:c r="D12" s="12" t="str">
+      <x:c r="D12" s="10" t="str">
         <x:v>Kaktus</x:v>
       </x:c>
-      <x:c r="E12" s="12" t="str">
+      <x:c r="E12" s="10" t="str">
         <x:v>Karla Kaktus</x:v>
       </x:c>
-      <x:c r="F12" s="12" t="str">
+      <x:c r="F12" s="10" t="str">
         <x:v>9A</x:v>
       </x:c>
-      <x:c r="G12" s="12" t="str">
+      <x:c r="G12" s="10" t="str">
         <x:v>E011_karla_kaktus.png</x:v>
       </x:c>
-      <x:c r="H12" s="12" t="str">
+      <x:c r="H12" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E011_karla_kaktus.png</x:v>
       </x:c>
-      <x:c r="I12" s="12" t="str">
+      <x:c r="I12" s="10" t="str">
         <x:v>Kak…</x:v>
       </x:c>
-      <x:c r="J12" s="12" t="str">
+      <x:c r="J12" s="10" t="str">
         <x:v>Karla Kaktus</x:v>
       </x:c>
-      <x:c r="K12" s="12" t="str">
+      <x:c r="K12" s="10" t="str">
         <x:v>Stikker lidt, men kun når afleveringen mangler navn.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="12" t="str">
+      <x:c r="A13" s="10" t="str">
         <x:v>E012</x:v>
       </x:c>
-      <x:c r="B13" s="12" t="str">
+      <x:c r="B13" s="10" t="str">
         <x:v>E012</x:v>
       </x:c>
-      <x:c r="C13" s="12" t="str">
+      <x:c r="C13" s="10" t="str">
         <x:v>Leo</x:v>
       </x:c>
-      <x:c r="D13" s="12" t="str">
+      <x:c r="D13" s="10" t="str">
         <x:v>Lommefilosof</x:v>
       </x:c>
-      <x:c r="E13" s="12" t="str">
+      <x:c r="E13" s="10" t="str">
         <x:v>Leo Lommefilosof</x:v>
       </x:c>
-      <x:c r="F13" s="12" t="str">
+      <x:c r="F13" s="10" t="str">
         <x:v>9A</x:v>
       </x:c>
-      <x:c r="G13" s="12" t="str">
+      <x:c r="G13" s="10" t="str">
         <x:v>E012_leo_lommefilosof.png</x:v>
       </x:c>
-      <x:c r="H13" s="12" t="str">
+      <x:c r="H13" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E012_leo_lommefilosof.png</x:v>
       </x:c>
-      <x:c r="I13" s="12" t="str">
+      <x:c r="I13" s="10" t="str">
         <x:v>Lommef…</x:v>
       </x:c>
-      <x:c r="J13" s="12" t="str">
+      <x:c r="J13" s="10" t="str">
         <x:v>Leo Lommefilosof</x:v>
       </x:c>
-      <x:c r="K13" s="12" t="str">
+      <x:c r="K13" s="10" t="str">
         <x:v>Spørger: 'Men hvad ER egentlig frikvarter?'</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="12" t="str">
+      <x:c r="A14" s="10" t="str">
         <x:v>E013</x:v>
       </x:c>
-      <x:c r="B14" s="12" t="str">
+      <x:c r="B14" s="10" t="str">
         <x:v>E013</x:v>
       </x:c>
-      <x:c r="C14" s="12" t="str">
+      <x:c r="C14" s="10" t="str">
         <x:v>Mira</x:v>
       </x:c>
-      <x:c r="D14" s="12" t="str">
+      <x:c r="D14" s="10" t="str">
         <x:v>Marmelade</x:v>
       </x:c>
-      <x:c r="E14" s="12" t="str">
+      <x:c r="E14" s="10" t="str">
         <x:v>Mira Marmelade</x:v>
       </x:c>
-      <x:c r="F14" s="12" t="str">
+      <x:c r="F14" s="10" t="str">
         <x:v>9A</x:v>
       </x:c>
-      <x:c r="G14" s="12" t="str">
+      <x:c r="G14" s="10" t="str">
         <x:v>E013_mira_marmelade.png</x:v>
       </x:c>
-      <x:c r="H14" s="12" t="str">
+      <x:c r="H14" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E013_mira_marmelade.png</x:v>
       </x:c>
-      <x:c r="I14" s="12" t="str">
+      <x:c r="I14" s="10" t="str">
         <x:v>Marmel…</x:v>
       </x:c>
-      <x:c r="J14" s="12" t="str">
+      <x:c r="J14" s="10" t="str">
         <x:v>Mira Marmelade</x:v>
       </x:c>
-      <x:c r="K14" s="12" t="str">
+      <x:c r="K14" s="10" t="str">
         <x:v>Spreder ro på brødet og i klassen.</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="12" t="str">
+      <x:c r="A15" s="10" t="str">
         <x:v>E014</x:v>
       </x:c>
-      <x:c r="B15" s="12" t="str">
+      <x:c r="B15" s="10" t="str">
         <x:v>E014</x:v>
       </x:c>
-      <x:c r="C15" s="12" t="str">
+      <x:c r="C15" s="10" t="str">
         <x:v>Noah</x:v>
       </x:c>
-      <x:c r="D15" s="12" t="str">
+      <x:c r="D15" s="10" t="str">
         <x:v>Nørkle</x:v>
       </x:c>
-      <x:c r="E15" s="12" t="str">
+      <x:c r="E15" s="10" t="str">
         <x:v>Noah Nørkle</x:v>
       </x:c>
-      <x:c r="F15" s="12" t="str">
+      <x:c r="F15" s="10" t="str">
         <x:v>9A</x:v>
       </x:c>
-      <x:c r="G15" s="12" t="str">
+      <x:c r="G15" s="10" t="str">
         <x:v>E014_noah_noerkle.png</x:v>
       </x:c>
-      <x:c r="H15" s="12" t="str">
+      <x:c r="H15" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E014_noah_noerkle.png</x:v>
       </x:c>
-      <x:c r="I15" s="12" t="str">
+      <x:c r="I15" s="10" t="str">
         <x:v>Nør…</x:v>
       </x:c>
-      <x:c r="J15" s="12" t="str">
+      <x:c r="J15" s="10" t="str">
         <x:v>Noah Nørkle</x:v>
       </x:c>
-      <x:c r="K15" s="12" t="str">
+      <x:c r="K15" s="10" t="str">
         <x:v>Bygger løsninger af tape, tegnestifter og optimisme.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="12" t="str">
+      <x:c r="A16" s="10" t="str">
         <x:v>E015</x:v>
       </x:c>
-      <x:c r="B16" s="12" t="str">
+      <x:c r="B16" s="10" t="str">
         <x:v>E015</x:v>
       </x:c>
-      <x:c r="C16" s="12" t="str">
+      <x:c r="C16" s="10" t="str">
         <x:v>Oda</x:v>
       </x:c>
-      <x:c r="D16" s="12" t="str">
+      <x:c r="D16" s="10" t="str">
         <x:v>Overspringsen</x:v>
       </x:c>
-      <x:c r="E16" s="12" t="str">
+      <x:c r="E16" s="10" t="str">
         <x:v>Oda Overspringsen</x:v>
       </x:c>
-      <x:c r="F16" s="12" t="str">
+      <x:c r="F16" s="10" t="str">
         <x:v>9A</x:v>
       </x:c>
-      <x:c r="G16" s="12" t="str">
+      <x:c r="G16" s="10" t="str">
         <x:v>E015_oda_overspringsen.png</x:v>
       </x:c>
-      <x:c r="H16" s="12" t="str">
+      <x:c r="H16" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E015_oda_overspringsen.png</x:v>
       </x:c>
-      <x:c r="I16" s="12" t="str">
+      <x:c r="I16" s="10" t="str">
         <x:v>Oversp…</x:v>
       </x:c>
-      <x:c r="J16" s="12" t="str">
+      <x:c r="J16" s="10" t="str">
         <x:v>Oda Overspringsen</x:v>
       </x:c>
-      <x:c r="K16" s="12" t="str">
+      <x:c r="K16" s="10" t="str">
         <x:v>Skulle lige noget vigtigt, men nåede det alligevel.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="12" t="str">
+      <x:c r="A17" s="10" t="str">
         <x:v>E016</x:v>
       </x:c>
-      <x:c r="B17" s="12" t="str">
+      <x:c r="B17" s="10" t="str">
         <x:v>E016</x:v>
       </x:c>
-      <x:c r="C17" s="12" t="str">
+      <x:c r="C17" s="10" t="str">
         <x:v>Pelle</x:v>
       </x:c>
-      <x:c r="D17" s="12" t="str">
+      <x:c r="D17" s="10" t="str">
         <x:v>Papirfly</x:v>
       </x:c>
-      <x:c r="E17" s="12" t="str">
+      <x:c r="E17" s="10" t="str">
         <x:v>Pelle Papirfly</x:v>
       </x:c>
-      <x:c r="F17" s="12" t="str">
+      <x:c r="F17" s="10" t="str">
         <x:v>9B</x:v>
       </x:c>
-      <x:c r="G17" s="12" t="str">
+      <x:c r="G17" s="10" t="str">
         <x:v>E016_pelle_papirfly.png</x:v>
       </x:c>
-      <x:c r="H17" s="12" t="str">
+      <x:c r="H17" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E016_pelle_papirfly.png</x:v>
       </x:c>
-      <x:c r="I17" s="12" t="str">
+      <x:c r="I17" s="10" t="str">
         <x:v>Papirf…</x:v>
       </x:c>
-      <x:c r="J17" s="12" t="str">
+      <x:c r="J17" s="10" t="str">
         <x:v>Pelle Papirfly</x:v>
       </x:c>
-      <x:c r="K17" s="12" t="str">
+      <x:c r="K17" s="10" t="str">
         <x:v>Afleverer helst i aerodynamisk format.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="12" t="str">
+      <x:c r="A18" s="10" t="str">
         <x:v>E017</x:v>
       </x:c>
-      <x:c r="B18" s="12" t="str">
+      <x:c r="B18" s="10" t="str">
         <x:v>E017</x:v>
       </x:c>
-      <x:c r="C18" s="12" t="str">
+      <x:c r="C18" s="10" t="str">
         <x:v>Quinten</x:v>
       </x:c>
-      <x:c r="D18" s="12" t="str">
+      <x:c r="D18" s="10" t="str">
         <x:v>Quizgaard</x:v>
       </x:c>
-      <x:c r="E18" s="12" t="str">
+      <x:c r="E18" s="10" t="str">
         <x:v>Quinten Quizgaard</x:v>
       </x:c>
-      <x:c r="F18" s="12" t="str">
+      <x:c r="F18" s="10" t="str">
         <x:v>9B</x:v>
       </x:c>
-      <x:c r="G18" s="12" t="str">
+      <x:c r="G18" s="10" t="str">
         <x:v>E017_quinten_quizgaard.png</x:v>
       </x:c>
-      <x:c r="H18" s="12" t="str">
+      <x:c r="H18" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E017_quinten_quizgaard.png</x:v>
       </x:c>
-      <x:c r="I18" s="12" t="str">
+      <x:c r="I18" s="10" t="str">
         <x:v>Quizga…</x:v>
       </x:c>
-      <x:c r="J18" s="12" t="str">
+      <x:c r="J18" s="10" t="str">
         <x:v>Quinten Quizgaard</x:v>
       </x:c>
-      <x:c r="K18" s="12" t="str">
+      <x:c r="K18" s="10" t="str">
         <x:v>Ved svaret før spørgsmålet er færdigt.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="12" t="str">
+      <x:c r="A19" s="10" t="str">
         <x:v>E018</x:v>
       </x:c>
-      <x:c r="B19" s="12" t="str">
+      <x:c r="B19" s="10" t="str">
         <x:v>E018</x:v>
       </x:c>
-      <x:c r="C19" s="12" t="str">
+      <x:c r="C19" s="10" t="str">
         <x:v>Rosa</x:v>
       </x:c>
-      <x:c r="D19" s="12" t="str">
+      <x:c r="D19" s="10" t="str">
         <x:v>Rundstykke</x:v>
       </x:c>
-      <x:c r="E19" s="12" t="str">
+      <x:c r="E19" s="10" t="str">
         <x:v>Rosa Rundstykke</x:v>
       </x:c>
-      <x:c r="F19" s="12" t="str">
+      <x:c r="F19" s="10" t="str">
         <x:v>9B</x:v>
       </x:c>
-      <x:c r="G19" s="12" t="str">
+      <x:c r="G19" s="10" t="str">
         <x:v>E018_rosa_rundstykke.png</x:v>
       </x:c>
-      <x:c r="H19" s="12" t="str">
+      <x:c r="H19" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E018_rosa_rundstykke.png</x:v>
       </x:c>
-      <x:c r="I19" s="12" t="str">
+      <x:c r="I19" s="10" t="str">
         <x:v>Rundst…</x:v>
       </x:c>
-      <x:c r="J19" s="12" t="str">
+      <x:c r="J19" s="10" t="str">
         <x:v>Rosa Rundstykke</x:v>
       </x:c>
-      <x:c r="K19" s="12" t="str">
+      <x:c r="K19" s="10" t="str">
         <x:v>Møder ind med sprød stemning og smør på humøret.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="12" t="str">
+      <x:c r="A20" s="10" t="str">
         <x:v>E019</x:v>
       </x:c>
-      <x:c r="B20" s="12" t="str">
+      <x:c r="B20" s="10" t="str">
         <x:v>E019</x:v>
       </x:c>
-      <x:c r="C20" s="12" t="str">
+      <x:c r="C20" s="10" t="str">
         <x:v>Silas</x:v>
       </x:c>
-      <x:c r="D20" s="12" t="str">
+      <x:c r="D20" s="10" t="str">
         <x:v>Snebold</x:v>
       </x:c>
-      <x:c r="E20" s="12" t="str">
+      <x:c r="E20" s="10" t="str">
         <x:v>Silas Snebold</x:v>
       </x:c>
-      <x:c r="F20" s="12" t="str">
+      <x:c r="F20" s="10" t="str">
         <x:v>9B</x:v>
       </x:c>
-      <x:c r="G20" s="12" t="str">
+      <x:c r="G20" s="10" t="str">
         <x:v>E019_silas_snebold.png</x:v>
       </x:c>
-      <x:c r="H20" s="12" t="str">
+      <x:c r="H20" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E019_silas_snebold.png</x:v>
       </x:c>
-      <x:c r="I20" s="12" t="str">
+      <x:c r="I20" s="10" t="str">
         <x:v>Snebol…</x:v>
       </x:c>
-      <x:c r="J20" s="12" t="str">
+      <x:c r="J20" s="10" t="str">
         <x:v>Silas Snebold</x:v>
       </x:c>
-      <x:c r="K20" s="12" t="str">
+      <x:c r="K20" s="10" t="str">
         <x:v>Kaster med idéer, ikke med skyld.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="12" t="str">
+      <x:c r="A21" s="10" t="str">
         <x:v>E020</x:v>
       </x:c>
-      <x:c r="B21" s="12" t="str">
+      <x:c r="B21" s="10" t="str">
         <x:v>E020</x:v>
       </x:c>
-      <x:c r="C21" s="12" t="str">
+      <x:c r="C21" s="10" t="str">
         <x:v>Tilde</x:v>
       </x:c>
-      <x:c r="D21" s="12" t="str">
+      <x:c r="D21" s="10" t="str">
         <x:v>Tidsmaskine</x:v>
       </x:c>
-      <x:c r="E21" s="12" t="str">
+      <x:c r="E21" s="10" t="str">
         <x:v>Tilde Tidsmaskine</x:v>
       </x:c>
-      <x:c r="F21" s="12" t="str">
+      <x:c r="F21" s="10" t="str">
         <x:v>9B</x:v>
       </x:c>
-      <x:c r="G21" s="12" t="str">
+      <x:c r="G21" s="10" t="str">
         <x:v>E020_tilde_tidsmaskine.png</x:v>
       </x:c>
-      <x:c r="H21" s="12" t="str">
+      <x:c r="H21" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E020_tilde_tidsmaskine.png</x:v>
       </x:c>
-      <x:c r="I21" s="12" t="str">
+      <x:c r="I21" s="10" t="str">
         <x:v>Tidsma…</x:v>
       </x:c>
-      <x:c r="J21" s="12" t="str">
+      <x:c r="J21" s="10" t="str">
         <x:v>Tilde Tidsmaskine</x:v>
       </x:c>
-      <x:c r="K21" s="12" t="str">
+      <x:c r="K21" s="10" t="str">
         <x:v>Kommer for sent, men påstår hun var tidligt i 2034.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="12" t="str">
+      <x:c r="A22" s="10" t="str">
         <x:v>E021</x:v>
       </x:c>
-      <x:c r="B22" s="12" t="str">
+      <x:c r="B22" s="10" t="str">
         <x:v>E021</x:v>
       </x:c>
-      <x:c r="C22" s="12" t="str">
+      <x:c r="C22" s="10" t="str">
         <x:v>Ulrik</x:v>
       </x:c>
-      <x:c r="D22" s="12" t="str">
+      <x:c r="D22" s="10" t="str">
         <x:v>Uglebjerg</x:v>
       </x:c>
-      <x:c r="E22" s="12" t="str">
+      <x:c r="E22" s="10" t="str">
         <x:v>Ulrik Uglebjerg</x:v>
       </x:c>
-      <x:c r="F22" s="12" t="str">
+      <x:c r="F22" s="10" t="str">
         <x:v>10A</x:v>
       </x:c>
-      <x:c r="G22" s="12" t="str">
+      <x:c r="G22" s="10" t="str">
         <x:v>E021_ulrik_uglebjerg.png</x:v>
       </x:c>
-      <x:c r="H22" s="12" t="str">
+      <x:c r="H22" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E021_ulrik_uglebjerg.png</x:v>
       </x:c>
-      <x:c r="I22" s="12" t="str">
+      <x:c r="I22" s="10" t="str">
         <x:v>Uglebj…</x:v>
       </x:c>
-      <x:c r="J22" s="12" t="str">
+      <x:c r="J22" s="10" t="str">
         <x:v>Ulrik Uglebjerg</x:v>
       </x:c>
-      <x:c r="K22" s="12" t="str">
+      <x:c r="K22" s="10" t="str">
         <x:v>Vågen når andre lukker fanerne.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="12" t="str">
+      <x:c r="A23" s="10" t="str">
         <x:v>E022</x:v>
       </x:c>
-      <x:c r="B23" s="12" t="str">
+      <x:c r="B23" s="10" t="str">
         <x:v>E022</x:v>
       </x:c>
-      <x:c r="C23" s="12" t="str">
+      <x:c r="C23" s="10" t="str">
         <x:v>Vera</x:v>
       </x:c>
-      <x:c r="D23" s="12" t="str">
+      <x:c r="D23" s="10" t="str">
         <x:v>Vaffelvang</x:v>
       </x:c>
-      <x:c r="E23" s="12" t="str">
+      <x:c r="E23" s="10" t="str">
         <x:v>Vera Vaffelvang</x:v>
       </x:c>
-      <x:c r="F23" s="12" t="str">
+      <x:c r="F23" s="10" t="str">
         <x:v>10A</x:v>
       </x:c>
-      <x:c r="G23" s="12" t="str">
+      <x:c r="G23" s="10" t="str">
         <x:v>E022_vera_vaffelvang.png</x:v>
       </x:c>
-      <x:c r="H23" s="12" t="str">
+      <x:c r="H23" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E022_vera_vaffelvang.png</x:v>
       </x:c>
-      <x:c r="I23" s="12" t="str">
+      <x:c r="I23" s="10" t="str">
         <x:v>Vaffel…</x:v>
       </x:c>
-      <x:c r="J23" s="12" t="str">
+      <x:c r="J23" s="10" t="str">
         <x:v>Vera Vaffelvang</x:v>
       </x:c>
-      <x:c r="K23" s="12" t="str">
+      <x:c r="K23" s="10" t="str">
         <x:v>Kan gøre enhver diskussion firkantet på den gode måde.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="12" t="str">
+      <x:c r="A24" s="10" t="str">
         <x:v>E023</x:v>
       </x:c>
-      <x:c r="B24" s="12" t="str">
+      <x:c r="B24" s="10" t="str">
         <x:v>E023</x:v>
       </x:c>
-      <x:c r="C24" s="12" t="str">
+      <x:c r="C24" s="10" t="str">
         <x:v>Wilma</x:v>
       </x:c>
-      <x:c r="D24" s="12" t="str">
+      <x:c r="D24" s="10" t="str">
         <x:v>WiFi</x:v>
       </x:c>
-      <x:c r="E24" s="12" t="str">
+      <x:c r="E24" s="10" t="str">
         <x:v>Wilma WiFi</x:v>
       </x:c>
-      <x:c r="F24" s="12" t="str">
+      <x:c r="F24" s="10" t="str">
         <x:v>10A</x:v>
       </x:c>
-      <x:c r="G24" s="12" t="str">
+      <x:c r="G24" s="10" t="str">
         <x:v>E023_wilma_wifi.png</x:v>
       </x:c>
-      <x:c r="H24" s="12" t="str">
+      <x:c r="H24" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E023_wilma_wifi.png</x:v>
       </x:c>
-      <x:c r="I24" s="12" t="str">
+      <x:c r="I24" s="10" t="str">
         <x:v>WiF…</x:v>
       </x:c>
-      <x:c r="J24" s="12" t="str">
+      <x:c r="J24" s="10" t="str">
         <x:v>Wilma WiFi</x:v>
       </x:c>
-      <x:c r="K24" s="12" t="str">
+      <x:c r="K24" s="10" t="str">
         <x:v>Forsvinder kort, men forbinder altid igen.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="12" t="str">
+      <x:c r="A25" s="10" t="str">
         <x:v>E024</x:v>
       </x:c>
-      <x:c r="B25" s="12" t="str">
+      <x:c r="B25" s="10" t="str">
         <x:v>E024</x:v>
       </x:c>
-      <x:c r="C25" s="12" t="str">
+      <x:c r="C25" s="10" t="str">
         <x:v>Xander</x:v>
       </x:c>
-      <x:c r="D25" s="12" t="str">
+      <x:c r="D25" s="10" t="str">
         <x:v>Xylofon</x:v>
       </x:c>
-      <x:c r="E25" s="12" t="str">
+      <x:c r="E25" s="10" t="str">
         <x:v>Xander Xylofon</x:v>
       </x:c>
-      <x:c r="F25" s="12" t="str">
+      <x:c r="F25" s="10" t="str">
         <x:v>10A</x:v>
       </x:c>
-      <x:c r="G25" s="12" t="str">
+      <x:c r="G25" s="10" t="str">
         <x:v>E024_xander_xylofon.png</x:v>
       </x:c>
-      <x:c r="H25" s="12" t="str">
+      <x:c r="H25" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E024_xander_xylofon.png</x:v>
       </x:c>
-      <x:c r="I25" s="12" t="str">
+      <x:c r="I25" s="10" t="str">
         <x:v>Xylofo…</x:v>
       </x:c>
-      <x:c r="J25" s="12" t="str">
+      <x:c r="J25" s="10" t="str">
         <x:v>Xander Xylofon</x:v>
       </x:c>
-      <x:c r="K25" s="12" t="str">
+      <x:c r="K25" s="10" t="str">
         <x:v>Tænker i toner, selv i matematik.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="12" t="str">
+      <x:c r="A26" s="10" t="str">
         <x:v>E025</x:v>
       </x:c>
-      <x:c r="B26" s="12" t="str">
+      <x:c r="B26" s="10" t="str">
         <x:v>E025</x:v>
       </x:c>
-      <x:c r="C26" s="12" t="str">
+      <x:c r="C26" s="10" t="str">
         <x:v>Yrsa</x:v>
       </x:c>
-      <x:c r="D26" s="12" t="str">
+      <x:c r="D26" s="10" t="str">
         <x:v>Yoghurt</x:v>
       </x:c>
-      <x:c r="E26" s="12" t="str">
+      <x:c r="E26" s="10" t="str">
         <x:v>Yrsa Yoghurt</x:v>
       </x:c>
-      <x:c r="F26" s="12" t="str">
+      <x:c r="F26" s="10" t="str">
         <x:v>10A</x:v>
       </x:c>
-      <x:c r="G26" s="12" t="str">
+      <x:c r="G26" s="10" t="str">
         <x:v>E025_yrsa_yoghurt.png</x:v>
       </x:c>
-      <x:c r="H26" s="12" t="str">
+      <x:c r="H26" s="10" t="str">
         <x:v>navneleg-demo/students/photos/E025_yrsa_yoghurt.png</x:v>
       </x:c>
-      <x:c r="I26" s="12" t="str">
+      <x:c r="I26" s="10" t="str">
         <x:v>Yoghur…</x:v>
       </x:c>
-      <x:c r="J26" s="12" t="str">
+      <x:c r="J26" s="10" t="str">
         <x:v>Yrsa Yoghurt</x:v>
       </x:c>
-      <x:c r="K26" s="12" t="str">
+      <x:c r="K26" s="10" t="str">
         <x:v>Holder hovedet koldt og kulturen levende.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad35e095d63f4ea2"/>
+  </x:tableParts>
 </x:worksheet>
 </file>